--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,10 +75,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,7 +448,7 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>470</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>470</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4">
@@ -497,11 +497,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Skipped Test Cases</t>
+          <t>Skipped / Blocked Test Cases</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 11:43:23</t>
+          <t>2026-08-28 14:43:36</t>
         </is>
       </c>
     </row>

--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 14:43:36</t>
+          <t>2026-08-28 14:53:52</t>
         </is>
       </c>
     </row>
